--- a/app/模板/结算模板/【大连游者之家】结算单_战双版更需求26年5月模板.xlsx
+++ b/app/模板/结算模板/【大连游者之家】结算单_战双版更需求26年5月模板.xlsx
@@ -96,13 +96,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0085B4"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">公司名称： </t>
     </r>
     <r>
@@ -155,7 +148,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 现代服务*翻译服务费
+      <t xml:space="preserve"> 生产生活服务*翻译服务
 </t>
     </r>
     <r>
@@ -1705,7 +1698,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="895350" y="8886825"/>
+          <a:off x="895350" y="8896350"/>
           <a:ext cx="1189990" cy="953770"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2091,7 +2084,7 @@
       <c r="G9" s="19"/>
       <c r="H9" s="20"/>
     </row>
-    <row r="10" spans="2:18">
+    <row r="10" ht="14.25" spans="2:18">
       <c r="B10" s="9" t="s">
         <v>11</v>
       </c>
